--- a/informes_data/Tercera FEB/2025-26/Regular_Season/individual/NP_play_by_play_2484265_PROCESSED_CHRONO.xlsx
+++ b/informes_data/Tercera FEB/2025-26/Regular_Season/individual/NP_play_by_play_2484265_PROCESSED_CHRONO.xlsx
@@ -565,13 +565,13 @@
         <v>1</v>
       </c>
       <c r="D2" t="n">
-        <v>5.5656</v>
+        <v>6.978</v>
       </c>
       <c r="E2" t="n">
-        <v>5.1404</v>
+        <v>6.1715</v>
       </c>
       <c r="F2" t="n">
-        <v>0.4252</v>
+        <v>0.8065</v>
       </c>
       <c r="G2" t="n">
         <v>1.3603</v>
@@ -610,13 +610,13 @@
         <v>2.9301</v>
       </c>
       <c r="S2" t="n">
-        <v>-1.0719</v>
+        <v>0.3405</v>
       </c>
       <c r="T2" t="n">
-        <v>-0.839</v>
+        <v>0.1921</v>
       </c>
       <c r="U2" t="n">
-        <v>-0.2329</v>
+        <v>0.1484</v>
       </c>
       <c r="V2" t="n">
         <v>3.3238</v>
@@ -643,13 +643,13 @@
         <v>1</v>
       </c>
       <c r="D3" t="n">
-        <v>4.7915</v>
+        <v>3.4911</v>
       </c>
       <c r="E3" t="n">
-        <v>2.6287</v>
+        <v>1.9002</v>
       </c>
       <c r="F3" t="n">
-        <v>2.1629</v>
+        <v>1.5909</v>
       </c>
       <c r="G3" t="n">
         <v>0.829</v>
@@ -688,13 +688,13 @@
         <v>2.7348</v>
       </c>
       <c r="S3" t="n">
-        <v>1.9077</v>
+        <v>0.6073</v>
       </c>
       <c r="T3" t="n">
-        <v>0.8669</v>
+        <v>0.1385</v>
       </c>
       <c r="U3" t="n">
-        <v>1.0408</v>
+        <v>0.4688</v>
       </c>
       <c r="V3" t="n">
         <v>1.2735</v>
@@ -721,13 +721,13 @@
         <v>1</v>
       </c>
       <c r="D4" t="n">
-        <v>3.2072</v>
+        <v>3.4039</v>
       </c>
       <c r="E4" t="n">
-        <v>2.1941</v>
+        <v>2.2547</v>
       </c>
       <c r="F4" t="n">
-        <v>1.0131</v>
+        <v>1.1493</v>
       </c>
       <c r="G4" t="n">
         <v>0.1492</v>
@@ -766,13 +766,13 @@
         <v>2.1488</v>
       </c>
       <c r="S4" t="n">
-        <v>0.2999</v>
+        <v>0.4966</v>
       </c>
       <c r="T4" t="n">
-        <v>0.0497</v>
+        <v>0.1102</v>
       </c>
       <c r="U4" t="n">
-        <v>0.2502</v>
+        <v>0.3864</v>
       </c>
       <c r="V4" t="n">
         <v>0.6093</v>
@@ -799,13 +799,13 @@
         <v>1</v>
       </c>
       <c r="D5" t="n">
-        <v>2.0299</v>
+        <v>2.3905</v>
       </c>
       <c r="E5" t="n">
-        <v>2.6047</v>
+        <v>2.584</v>
       </c>
       <c r="F5" t="n">
-        <v>-0.5748</v>
+        <v>-0.1935</v>
       </c>
       <c r="G5" t="n">
         <v>2.9041</v>
@@ -844,13 +844,13 @@
         <v>1.3674</v>
       </c>
       <c r="S5" t="n">
-        <v>-0.3235</v>
+        <v>0.0371</v>
       </c>
       <c r="T5" t="n">
-        <v>0.1102</v>
+        <v>0.0895</v>
       </c>
       <c r="U5" t="n">
-        <v>-0.4337</v>
+        <v>-0.0524</v>
       </c>
       <c r="V5" t="n">
         <v>-0.9414</v>
@@ -877,13 +877,13 @@
         <v>1</v>
       </c>
       <c r="D6" t="n">
-        <v>1.7838</v>
+        <v>0.8097</v>
       </c>
       <c r="E6" t="n">
-        <v>0.4944</v>
+        <v>-0.1529</v>
       </c>
       <c r="F6" t="n">
-        <v>1.2895</v>
+        <v>0.9627</v>
       </c>
       <c r="G6" t="n">
         <v>-0.3638</v>
@@ -922,13 +922,13 @@
         <v>2.3441</v>
       </c>
       <c r="S6" t="n">
-        <v>2.4564</v>
+        <v>1.4823</v>
       </c>
       <c r="T6" t="n">
-        <v>1.109</v>
+        <v>0.4618</v>
       </c>
       <c r="U6" t="n">
-        <v>1.3474</v>
+        <v>1.0205</v>
       </c>
       <c r="V6" t="n">
         <v>0.2772</v>
@@ -955,13 +955,13 @@
         <v>1</v>
       </c>
       <c r="D7" t="n">
-        <v>-1.9732</v>
+        <v>-1.7783</v>
       </c>
       <c r="E7" t="n">
-        <v>-1.9597</v>
+        <v>-1.7375</v>
       </c>
       <c r="F7" t="n">
-        <v>-0.0135</v>
+        <v>-0.0408</v>
       </c>
       <c r="G7" t="n">
         <v>-0.8435</v>
@@ -1000,13 +1000,13 @@
         <v>0.3907</v>
       </c>
       <c r="S7" t="n">
-        <v>-0.5437</v>
+        <v>-0.3487</v>
       </c>
       <c r="T7" t="n">
-        <v>-0.3494</v>
+        <v>-0.1272</v>
       </c>
       <c r="U7" t="n">
-        <v>-0.1943</v>
+        <v>-0.2215</v>
       </c>
       <c r="V7" t="n">
         <v>0</v>
@@ -1033,13 +1033,13 @@
         <v>1</v>
       </c>
       <c r="D8" t="n">
-        <v>-2.49</v>
+        <v>-2.4022</v>
       </c>
       <c r="E8" t="n">
-        <v>-1.6103</v>
+        <v>-1.5498</v>
       </c>
       <c r="F8" t="n">
-        <v>-0.8796</v>
+        <v>-0.8524</v>
       </c>
       <c r="G8" t="n">
         <v>-1.5824</v>
@@ -1078,13 +1078,13 @@
         <v>0.1953</v>
       </c>
       <c r="S8" t="n">
-        <v>-0.4936</v>
+        <v>-0.4058</v>
       </c>
       <c r="T8" t="n">
-        <v>-0.3026</v>
+        <v>-0.2421</v>
       </c>
       <c r="U8" t="n">
-        <v>-0.191</v>
+        <v>-0.1637</v>
       </c>
       <c r="V8" t="n">
         <v>-0.6093</v>
@@ -1111,13 +1111,13 @@
         <v>1</v>
       </c>
       <c r="D9" t="n">
-        <v>-3.4945</v>
+        <v>-2.8333</v>
       </c>
       <c r="E9" t="n">
-        <v>-1.9864</v>
+        <v>-1.3797</v>
       </c>
       <c r="F9" t="n">
-        <v>-1.5081</v>
+        <v>-1.4536</v>
       </c>
       <c r="G9" t="n">
         <v>-4.0934</v>
@@ -1156,13 +1156,13 @@
         <v>1.5627</v>
       </c>
       <c r="S9" t="n">
-        <v>-0.5965</v>
+        <v>0.06469999999999999</v>
       </c>
       <c r="T9" t="n">
-        <v>-0.4566</v>
+        <v>0.1501</v>
       </c>
       <c r="U9" t="n">
-        <v>-0.1398</v>
+        <v>-0.0854</v>
       </c>
       <c r="V9" t="n">
         <v>0.6093</v>
@@ -1189,13 +1189,13 @@
         <v>1</v>
       </c>
       <c r="D10" t="n">
-        <v>-4.0592</v>
+        <v>-3.7904</v>
       </c>
       <c r="E10" t="n">
-        <v>-2.2182</v>
+        <v>-1.8949</v>
       </c>
       <c r="F10" t="n">
-        <v>-1.841</v>
+        <v>-1.8955</v>
       </c>
       <c r="G10" t="n">
         <v>-4.4506</v>
@@ -1234,13 +1234,13 @@
         <v>1.9534</v>
       </c>
       <c r="S10" t="n">
-        <v>-0.2179</v>
+        <v>0.0509</v>
       </c>
       <c r="T10" t="n">
-        <v>0.1707</v>
+        <v>0.494</v>
       </c>
       <c r="U10" t="n">
-        <v>-0.3886</v>
+        <v>-0.4431</v>
       </c>
       <c r="V10" t="n">
         <v>0.6093</v>
@@ -1267,13 +1267,13 @@
         <v>1</v>
       </c>
       <c r="D11" t="n">
-        <v>5.361099999999998</v>
+        <v>6.269</v>
       </c>
       <c r="E11" t="n">
-        <v>5.287699999999999</v>
+        <v>6.195599999999999</v>
       </c>
       <c r="F11" t="n">
-        <v>0.07369999999999965</v>
+        <v>0.07360000000000011</v>
       </c>
       <c r="G11" t="n">
         <v>-6.091099999999999</v>
@@ -1312,13 +1312,13 @@
         <v>15.6273</v>
       </c>
       <c r="S11" t="n">
-        <v>1.4169</v>
+        <v>2.3249</v>
       </c>
       <c r="T11" t="n">
-        <v>0.3589000000000001</v>
+        <v>1.2669</v>
       </c>
       <c r="U11" t="n">
-        <v>1.0581</v>
+        <v>1.058</v>
       </c>
       <c r="V11" t="n">
         <v>5.1517</v>
@@ -1345,13 +1345,13 @@
         <v>1</v>
       </c>
       <c r="D12" t="n">
-        <v>5.8809</v>
+        <v>6.2761</v>
       </c>
       <c r="E12" t="n">
-        <v>5.5834</v>
+        <v>5.6845</v>
       </c>
       <c r="F12" t="n">
-        <v>0.2974</v>
+        <v>0.5916</v>
       </c>
       <c r="G12" t="n">
         <v>5.2594</v>
@@ -1390,13 +1390,13 @@
         <v>0.9767</v>
       </c>
       <c r="S12" t="n">
-        <v>-0.0232</v>
+        <v>0.3721</v>
       </c>
       <c r="T12" t="n">
-        <v>0.0221</v>
+        <v>0.1232</v>
       </c>
       <c r="U12" t="n">
-        <v>-0.0453</v>
+        <v>0.2489</v>
       </c>
       <c r="V12" t="n">
         <v>-0.3321</v>
@@ -1423,13 +1423,13 @@
         <v>1</v>
       </c>
       <c r="D13" t="n">
-        <v>2.6759</v>
+        <v>2.5295</v>
       </c>
       <c r="E13" t="n">
-        <v>3.819</v>
+        <v>3.2123</v>
       </c>
       <c r="F13" t="n">
-        <v>-1.1432</v>
+        <v>-0.6829</v>
       </c>
       <c r="G13" t="n">
         <v>1.8628</v>
@@ -1468,13 +1468,13 @@
         <v>0.586</v>
       </c>
       <c r="S13" t="n">
-        <v>0.5591</v>
+        <v>0.4127</v>
       </c>
       <c r="T13" t="n">
-        <v>1.1199</v>
+        <v>0.5132</v>
       </c>
       <c r="U13" t="n">
-        <v>-0.5608</v>
+        <v>-0.1005</v>
       </c>
       <c r="V13" t="n">
         <v>-0.3321</v>
@@ -1501,13 +1501,13 @@
         <v>1</v>
       </c>
       <c r="D14" t="n">
-        <v>1.6932</v>
+        <v>1.4328</v>
       </c>
       <c r="E14" t="n">
-        <v>1.2841</v>
+        <v>0.374</v>
       </c>
       <c r="F14" t="n">
-        <v>0.4091</v>
+        <v>1.0587</v>
       </c>
       <c r="G14" t="n">
         <v>2.8283</v>
@@ -1546,13 +1546,13 @@
         <v>1.1721</v>
       </c>
       <c r="S14" t="n">
-        <v>0.623</v>
+        <v>0.3625</v>
       </c>
       <c r="T14" t="n">
-        <v>1.0815</v>
+        <v>0.1715</v>
       </c>
       <c r="U14" t="n">
-        <v>-0.4585</v>
+        <v>0.1911</v>
       </c>
       <c r="V14" t="n">
         <v>0</v>
@@ -1567,7 +1567,7 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>M. FENÉS HERNÁNDEZ</t>
+          <t>A. SAMAKE EL ALAOUI</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
@@ -1579,73 +1579,73 @@
         <v>1</v>
       </c>
       <c r="D15" t="n">
-        <v>0.1953</v>
+        <v>0.6819</v>
       </c>
       <c r="E15" t="n">
-        <v>0</v>
+        <v>-0.6214</v>
       </c>
       <c r="F15" t="n">
-        <v>0.1953</v>
+        <v>1.3033</v>
       </c>
       <c r="G15" t="n">
-        <v>0</v>
+        <v>1.0067</v>
       </c>
       <c r="H15" t="n">
-        <v>0</v>
+        <v>2.5306</v>
       </c>
       <c r="I15" t="n">
-        <v>0</v>
+        <v>-1.5239</v>
       </c>
       <c r="J15" t="n">
-        <v>0</v>
+        <v>0.9619</v>
       </c>
       <c r="K15" t="n">
-        <v>0</v>
+        <v>2.8895</v>
       </c>
       <c r="L15" t="n">
-        <v>0</v>
+        <v>-1.9275</v>
       </c>
       <c r="M15" t="n">
-        <v>0</v>
+        <v>0.0448</v>
       </c>
       <c r="N15" t="n">
-        <v>0</v>
+        <v>-0.3589</v>
       </c>
       <c r="O15" t="n">
-        <v>0</v>
+        <v>0.4037</v>
       </c>
       <c r="P15" t="n">
-        <v>0.1953</v>
+        <v>-0.7814</v>
       </c>
       <c r="Q15" t="n">
-        <v>0</v>
+        <v>-1.9534</v>
       </c>
       <c r="R15" t="n">
-        <v>0.1953</v>
+        <v>1.1721</v>
       </c>
       <c r="S15" t="n">
-        <v>0</v>
+        <v>0.1245</v>
       </c>
       <c r="T15" t="n">
-        <v>0</v>
+        <v>-0.5164</v>
       </c>
       <c r="U15" t="n">
-        <v>0</v>
+        <v>0.6409</v>
       </c>
       <c r="V15" t="n">
-        <v>0</v>
+        <v>0.3321</v>
       </c>
       <c r="W15" t="n">
-        <v>0</v>
+        <v>0.8865</v>
       </c>
       <c r="X15" t="n">
-        <v>0</v>
+        <v>-0.5545</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>A. SAMAKE EL ALAOUI</t>
+          <t>G. RUBIO GRACIA</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -1657,73 +1657,73 @@
         <v>1</v>
       </c>
       <c r="D16" t="n">
-        <v>0.0286</v>
+        <v>0.583</v>
       </c>
       <c r="E16" t="n">
-        <v>-0.9247</v>
+        <v>0.0931</v>
       </c>
       <c r="F16" t="n">
-        <v>0.9533</v>
+        <v>0.4899</v>
       </c>
       <c r="G16" t="n">
-        <v>1.0067</v>
+        <v>0.3614</v>
       </c>
       <c r="H16" t="n">
-        <v>2.5306</v>
+        <v>0.4285</v>
       </c>
       <c r="I16" t="n">
-        <v>-1.5239</v>
+        <v>-0.06710000000000001</v>
       </c>
       <c r="J16" t="n">
-        <v>0.9619</v>
+        <v>0.3867</v>
       </c>
       <c r="K16" t="n">
-        <v>2.8895</v>
+        <v>0.4528</v>
       </c>
       <c r="L16" t="n">
-        <v>-1.9275</v>
+        <v>-0.06610000000000001</v>
       </c>
       <c r="M16" t="n">
-        <v>0.0448</v>
+        <v>-0.0253</v>
       </c>
       <c r="N16" t="n">
-        <v>-0.3589</v>
+        <v>-0.0243</v>
       </c>
       <c r="O16" t="n">
-        <v>0.4037</v>
+        <v>-0.001</v>
       </c>
       <c r="P16" t="n">
-        <v>-0.7814</v>
+        <v>1.1721</v>
       </c>
       <c r="Q16" t="n">
-        <v>-1.9534</v>
+        <v>0</v>
       </c>
       <c r="R16" t="n">
         <v>1.1721</v>
       </c>
       <c r="S16" t="n">
-        <v>-0.5288</v>
+        <v>0.5454</v>
       </c>
       <c r="T16" t="n">
-        <v>-0.8198</v>
+        <v>-0.2935</v>
       </c>
       <c r="U16" t="n">
-        <v>0.2909</v>
+        <v>0.839</v>
       </c>
       <c r="V16" t="n">
-        <v>0.3321</v>
+        <v>-1.4959</v>
       </c>
       <c r="W16" t="n">
-        <v>0.8865</v>
+        <v>0</v>
       </c>
       <c r="X16" t="n">
-        <v>-0.5545</v>
+        <v>-1.4959</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>G. RUBIO GRACIA</t>
+          <t>M. FENÉS HERNÁNDEZ</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -1735,73 +1735,73 @@
         <v>1</v>
       </c>
       <c r="D17" t="n">
-        <v>-0.2855</v>
+        <v>0.1953</v>
       </c>
       <c r="E17" t="n">
-        <v>-0.6147</v>
+        <v>0</v>
       </c>
       <c r="F17" t="n">
-        <v>0.3292</v>
+        <v>0.1953</v>
       </c>
       <c r="G17" t="n">
-        <v>0.3614</v>
+        <v>0</v>
       </c>
       <c r="H17" t="n">
-        <v>0.4285</v>
+        <v>0</v>
       </c>
       <c r="I17" t="n">
-        <v>-0.06710000000000001</v>
+        <v>0</v>
       </c>
       <c r="J17" t="n">
-        <v>0.3867</v>
+        <v>0</v>
       </c>
       <c r="K17" t="n">
-        <v>0.4528</v>
+        <v>0</v>
       </c>
       <c r="L17" t="n">
-        <v>-0.06610000000000001</v>
+        <v>0</v>
       </c>
       <c r="M17" t="n">
-        <v>-0.0253</v>
+        <v>0</v>
       </c>
       <c r="N17" t="n">
-        <v>-0.0243</v>
+        <v>0</v>
       </c>
       <c r="O17" t="n">
-        <v>-0.001</v>
+        <v>0</v>
       </c>
       <c r="P17" t="n">
-        <v>1.1721</v>
+        <v>0.1953</v>
       </c>
       <c r="Q17" t="n">
         <v>0</v>
       </c>
       <c r="R17" t="n">
-        <v>1.1721</v>
+        <v>0.1953</v>
       </c>
       <c r="S17" t="n">
-        <v>-0.3231</v>
+        <v>0</v>
       </c>
       <c r="T17" t="n">
-        <v>-1.0013</v>
+        <v>0</v>
       </c>
       <c r="U17" t="n">
-        <v>0.6783</v>
+        <v>0</v>
       </c>
       <c r="V17" t="n">
-        <v>-1.4959</v>
+        <v>0</v>
       </c>
       <c r="W17" t="n">
         <v>0</v>
       </c>
       <c r="X17" t="n">
-        <v>-1.4959</v>
+        <v>0</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>R. PÉREZ GALINDO</t>
+          <t>B. MORALES CONILL</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -1813,73 +1813,73 @@
         <v>1</v>
       </c>
       <c r="D18" t="n">
-        <v>-0.6371</v>
+        <v>0.1093</v>
       </c>
       <c r="E18" t="n">
-        <v>2.5701</v>
+        <v>-0.8902</v>
       </c>
       <c r="F18" t="n">
-        <v>-3.2072</v>
+        <v>0.9995000000000001</v>
       </c>
       <c r="G18" t="n">
-        <v>0.6626</v>
+        <v>-0.1466</v>
       </c>
       <c r="H18" t="n">
-        <v>0.0023</v>
+        <v>-0.2407</v>
       </c>
       <c r="I18" t="n">
-        <v>0.6603</v>
+        <v>0.09420000000000001</v>
       </c>
       <c r="J18" t="n">
-        <v>3.0545</v>
+        <v>1.0273</v>
       </c>
       <c r="K18" t="n">
-        <v>1.7191</v>
+        <v>0.3927</v>
       </c>
       <c r="L18" t="n">
-        <v>1.3354</v>
+        <v>0.6346000000000001</v>
       </c>
       <c r="M18" t="n">
-        <v>-2.3919</v>
+        <v>-1.1739</v>
       </c>
       <c r="N18" t="n">
-        <v>-1.7168</v>
+        <v>-0.6334</v>
       </c>
       <c r="O18" t="n">
-        <v>-0.6751</v>
+        <v>-0.5405</v>
       </c>
       <c r="P18" t="n">
-        <v>0.1953</v>
+        <v>0</v>
       </c>
       <c r="Q18" t="n">
-        <v>-0.9767</v>
+        <v>-1.9534</v>
       </c>
       <c r="R18" t="n">
-        <v>1.1721</v>
+        <v>1.9534</v>
       </c>
       <c r="S18" t="n">
-        <v>-1.2178</v>
+        <v>0.2559</v>
       </c>
       <c r="T18" t="n">
-        <v>-0.7262999999999999</v>
+        <v>0.0359</v>
       </c>
       <c r="U18" t="n">
-        <v>-0.4915</v>
+        <v>0.22</v>
       </c>
       <c r="V18" t="n">
-        <v>-0.2772</v>
+        <v>0</v>
       </c>
       <c r="W18" t="n">
-        <v>1.2186</v>
+        <v>0</v>
       </c>
       <c r="X18" t="n">
-        <v>-1.4959</v>
+        <v>0</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>B. MORALES CONILL</t>
+          <t>R. PÉREZ GALINDO</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -1891,73 +1891,73 @@
         <v>1</v>
       </c>
       <c r="D19" t="n">
-        <v>-1.2389</v>
+        <v>0.0435</v>
       </c>
       <c r="E19" t="n">
-        <v>-1.6992</v>
+        <v>2.8735</v>
       </c>
       <c r="F19" t="n">
-        <v>0.4603</v>
+        <v>-2.83</v>
       </c>
       <c r="G19" t="n">
-        <v>-0.1466</v>
+        <v>0.6626</v>
       </c>
       <c r="H19" t="n">
-        <v>-0.2407</v>
+        <v>0.0023</v>
       </c>
       <c r="I19" t="n">
-        <v>0.09420000000000001</v>
+        <v>0.6603</v>
       </c>
       <c r="J19" t="n">
-        <v>1.0273</v>
+        <v>3.0545</v>
       </c>
       <c r="K19" t="n">
-        <v>0.3927</v>
+        <v>1.7191</v>
       </c>
       <c r="L19" t="n">
-        <v>0.6346000000000001</v>
+        <v>1.3354</v>
       </c>
       <c r="M19" t="n">
-        <v>-1.1739</v>
+        <v>-2.3919</v>
       </c>
       <c r="N19" t="n">
-        <v>-0.6334</v>
+        <v>-1.7168</v>
       </c>
       <c r="O19" t="n">
-        <v>-0.5405</v>
+        <v>-0.6751</v>
       </c>
       <c r="P19" t="n">
-        <v>0</v>
+        <v>0.1953</v>
       </c>
       <c r="Q19" t="n">
-        <v>-1.9534</v>
+        <v>-0.9767</v>
       </c>
       <c r="R19" t="n">
-        <v>1.9534</v>
+        <v>1.1721</v>
       </c>
       <c r="S19" t="n">
-        <v>-1.0923</v>
+        <v>-0.5372</v>
       </c>
       <c r="T19" t="n">
-        <v>-0.773</v>
+        <v>-0.4229</v>
       </c>
       <c r="U19" t="n">
-        <v>-0.3193</v>
+        <v>-0.1143</v>
       </c>
       <c r="V19" t="n">
-        <v>0</v>
+        <v>-0.2772</v>
       </c>
       <c r="W19" t="n">
-        <v>0</v>
+        <v>1.2186</v>
       </c>
       <c r="X19" t="n">
-        <v>0</v>
+        <v>-1.4959</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>G. PÉREZ LAYUNTA</t>
+          <t>M. OBIOLS PUIG</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
@@ -1969,73 +1969,73 @@
         <v>1</v>
       </c>
       <c r="D20" t="n">
-        <v>-4.0014</v>
+        <v>-4.3858</v>
       </c>
       <c r="E20" t="n">
-        <v>-2.2978</v>
+        <v>-4.0135</v>
       </c>
       <c r="F20" t="n">
-        <v>-1.7036</v>
+        <v>-0.3723</v>
       </c>
       <c r="G20" t="n">
-        <v>-2.2977</v>
+        <v>-1.5838</v>
       </c>
       <c r="H20" t="n">
-        <v>-1.2049</v>
+        <v>-1.3001</v>
       </c>
       <c r="I20" t="n">
-        <v>-1.0928</v>
+        <v>-0.2837</v>
       </c>
       <c r="J20" t="n">
-        <v>0.2992</v>
+        <v>-1.7781</v>
       </c>
       <c r="K20" t="n">
-        <v>0.3121</v>
+        <v>-1.2254</v>
       </c>
       <c r="L20" t="n">
-        <v>-0.0128</v>
+        <v>-0.5527</v>
       </c>
       <c r="M20" t="n">
-        <v>-2.5969</v>
+        <v>0.1944</v>
       </c>
       <c r="N20" t="n">
-        <v>-1.517</v>
+        <v>-0.0747</v>
       </c>
       <c r="O20" t="n">
-        <v>-1.0799</v>
+        <v>0.269</v>
       </c>
       <c r="P20" t="n">
-        <v>-1.7581</v>
+        <v>-1.5627</v>
       </c>
       <c r="Q20" t="n">
-        <v>-2.9301</v>
+        <v>-1.9534</v>
       </c>
       <c r="R20" t="n">
-        <v>1.1721</v>
+        <v>0.3907</v>
       </c>
       <c r="S20" t="n">
-        <v>0.6637</v>
+        <v>-0.0207</v>
       </c>
       <c r="T20" t="n">
-        <v>0.3331</v>
+        <v>-0.282</v>
       </c>
       <c r="U20" t="n">
-        <v>0.3306</v>
+        <v>0.2613</v>
       </c>
       <c r="V20" t="n">
-        <v>-0.6093</v>
+        <v>-1.2186</v>
       </c>
       <c r="W20" t="n">
         <v>0</v>
       </c>
       <c r="X20" t="n">
-        <v>-0.6093</v>
+        <v>-1.2186</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>M. OBIOLS PUIG</t>
+          <t>G. PÉREZ LAYUNTA</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
@@ -2047,67 +2047,67 @@
         <v>1</v>
       </c>
       <c r="D21" t="n">
-        <v>-4.7228</v>
+        <v>-4.52</v>
       </c>
       <c r="E21" t="n">
-        <v>-4.2157</v>
+        <v>-3.0056</v>
       </c>
       <c r="F21" t="n">
-        <v>-0.5071</v>
+        <v>-1.5143</v>
       </c>
       <c r="G21" t="n">
-        <v>-1.5838</v>
+        <v>-2.2977</v>
       </c>
       <c r="H21" t="n">
-        <v>-1.3001</v>
+        <v>-1.2049</v>
       </c>
       <c r="I21" t="n">
-        <v>-0.2837</v>
+        <v>-1.0928</v>
       </c>
       <c r="J21" t="n">
-        <v>-1.7781</v>
+        <v>0.2992</v>
       </c>
       <c r="K21" t="n">
-        <v>-1.2254</v>
+        <v>0.3121</v>
       </c>
       <c r="L21" t="n">
-        <v>-0.5527</v>
+        <v>-0.0128</v>
       </c>
       <c r="M21" t="n">
-        <v>0.1944</v>
+        <v>-2.5969</v>
       </c>
       <c r="N21" t="n">
-        <v>-0.0747</v>
+        <v>-1.517</v>
       </c>
       <c r="O21" t="n">
-        <v>0.269</v>
+        <v>-1.0799</v>
       </c>
       <c r="P21" t="n">
-        <v>-1.5627</v>
+        <v>-1.7581</v>
       </c>
       <c r="Q21" t="n">
-        <v>-1.9534</v>
+        <v>-2.9301</v>
       </c>
       <c r="R21" t="n">
-        <v>0.3907</v>
+        <v>1.1721</v>
       </c>
       <c r="S21" t="n">
-        <v>-0.3577</v>
+        <v>0.1452</v>
       </c>
       <c r="T21" t="n">
-        <v>-0.4842</v>
+        <v>-0.3747</v>
       </c>
       <c r="U21" t="n">
-        <v>0.1265</v>
+        <v>0.5199</v>
       </c>
       <c r="V21" t="n">
-        <v>-1.2186</v>
+        <v>-0.6093</v>
       </c>
       <c r="W21" t="n">
         <v>0</v>
       </c>
       <c r="X21" t="n">
-        <v>-1.2186</v>
+        <v>-0.6093</v>
       </c>
     </row>
     <row r="22">
@@ -2125,13 +2125,13 @@
         <v>1</v>
       </c>
       <c r="D22" t="n">
-        <v>-4.9494</v>
+        <v>-4.9364</v>
       </c>
       <c r="E22" t="n">
-        <v>-3.5782</v>
+        <v>-3.7804</v>
       </c>
       <c r="F22" t="n">
-        <v>-1.3712</v>
+        <v>-1.156</v>
       </c>
       <c r="G22" t="n">
         <v>-1.862</v>
@@ -2170,13 +2170,13 @@
         <v>0.7814</v>
       </c>
       <c r="S22" t="n">
-        <v>0.2801</v>
+        <v>0.293</v>
       </c>
       <c r="T22" t="n">
-        <v>0.1899</v>
+        <v>-0.0123</v>
       </c>
       <c r="U22" t="n">
-        <v>0.0902</v>
+        <v>0.3053</v>
       </c>
       <c r="V22" t="n">
         <v>-1.2186</v>
@@ -2203,19 +2203,19 @@
         <v>1</v>
       </c>
       <c r="D23" t="n">
-        <v>-5.3612</v>
+        <v>-1.990799999999997</v>
       </c>
       <c r="E23" t="n">
-        <v>-0.07369999999999965</v>
+        <v>-0.07370000000000188</v>
       </c>
       <c r="F23" t="n">
-        <v>-5.287699999999999</v>
+        <v>-1.9172</v>
       </c>
       <c r="G23" t="n">
-        <v>6.091099999999999</v>
+        <v>6.0911</v>
       </c>
       <c r="H23" t="n">
-        <v>2.0467</v>
+        <v>2.046700000000001</v>
       </c>
       <c r="I23" t="n">
         <v>4.044600000000001</v>
@@ -2236,10 +2236,10 @@
         <v>-6.6345</v>
       </c>
       <c r="O23" t="n">
-        <v>-0.007899999999999796</v>
+        <v>-0.007900000000000129</v>
       </c>
       <c r="P23" t="n">
-        <v>-4.8837</v>
+        <v>-4.883699999999999</v>
       </c>
       <c r="Q23" t="n">
         <v>-15.6272</v>
@@ -2248,13 +2248,13 @@
         <v>10.744</v>
       </c>
       <c r="S23" t="n">
-        <v>-1.417</v>
+        <v>1.9534</v>
       </c>
       <c r="T23" t="n">
-        <v>-1.0581</v>
+        <v>-1.058</v>
       </c>
       <c r="U23" t="n">
-        <v>-0.3588999999999999</v>
+        <v>3.0116</v>
       </c>
       <c r="V23" t="n">
         <v>-5.1517</v>

--- a/informes_data/Tercera FEB/2025-26/Regular_Season/individual/NP_play_by_play_2484265_PROCESSED_CHRONO.xlsx
+++ b/informes_data/Tercera FEB/2025-26/Regular_Season/individual/NP_play_by_play_2484265_PROCESSED_CHRONO.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:X23"/>
+  <dimension ref="A1:Y26"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -549,6 +549,11 @@
           <t>Def_FT</t>
         </is>
       </c>
+      <c r="Y1" s="1" t="inlineStr">
+        <is>
+          <t>Game_File</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
@@ -627,11 +632,16 @@
       <c r="X2" t="n">
         <v>0</v>
       </c>
+      <c r="Y2" t="inlineStr">
+        <is>
+          <t>play_by_play_2484265_PROCESSED_CHRONO.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>G. GARCÍA RIERA</t>
+          <t>G. GARCIA RIERA</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -704,6 +714,11 @@
       </c>
       <c r="X3" t="n">
         <v>0.0549</v>
+      </c>
+      <c r="Y3" t="inlineStr">
+        <is>
+          <t>play_by_play_2484265_PROCESSED_CHRONO.xlsx</t>
+        </is>
       </c>
     </row>
     <row r="4">
@@ -783,6 +798,11 @@
       <c r="X4" t="n">
         <v>-0.8865</v>
       </c>
+      <c r="Y4" t="inlineStr">
+        <is>
+          <t>play_by_play_2484265_PROCESSED_CHRONO.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
@@ -861,6 +881,11 @@
       <c r="X5" t="n">
         <v>-1.2186</v>
       </c>
+      <c r="Y5" t="inlineStr">
+        <is>
+          <t>play_by_play_2484265_PROCESSED_CHRONO.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
@@ -939,6 +964,11 @@
       <c r="X6" t="n">
         <v>0</v>
       </c>
+      <c r="Y6" t="inlineStr">
+        <is>
+          <t>play_by_play_2484265_PROCESSED_CHRONO.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
@@ -1017,6 +1047,11 @@
       <c r="X7" t="n">
         <v>0</v>
       </c>
+      <c r="Y7" t="inlineStr">
+        <is>
+          <t>play_by_play_2484265_PROCESSED_CHRONO.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
@@ -1095,6 +1130,11 @@
       <c r="X8" t="n">
         <v>-0.6093</v>
       </c>
+      <c r="Y8" t="inlineStr">
+        <is>
+          <t>play_by_play_2484265_PROCESSED_CHRONO.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
@@ -1173,6 +1213,11 @@
       <c r="X9" t="n">
         <v>0</v>
       </c>
+      <c r="Y9" t="inlineStr">
+        <is>
+          <t>play_by_play_2484265_PROCESSED_CHRONO.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
@@ -1251,6 +1296,11 @@
       <c r="X10" t="n">
         <v>-1.2186</v>
       </c>
+      <c r="Y10" t="inlineStr">
+        <is>
+          <t>play_by_play_2484265_PROCESSED_CHRONO.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
@@ -1329,6 +1379,7 @@
       <c r="X11" t="n">
         <v>-3.878099999999999</v>
       </c>
+      <c r="Y11" t="inlineStr"/>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
@@ -1407,11 +1458,16 @@
       <c r="X12" t="n">
         <v>-1.2186</v>
       </c>
+      <c r="Y12" t="inlineStr">
+        <is>
+          <t>play_by_play_2484265_PROCESSED_CHRONO.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>P. MARTÍNEZ FERIA</t>
+          <t>P. MARTINEZ FERIA</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
@@ -1423,31 +1479,31 @@
         <v>1</v>
       </c>
       <c r="D13" t="n">
-        <v>2.5295</v>
+        <v>1.6155</v>
       </c>
       <c r="E13" t="n">
-        <v>3.2123</v>
+        <v>2.2984</v>
       </c>
       <c r="F13" t="n">
         <v>-0.6829</v>
       </c>
       <c r="G13" t="n">
-        <v>1.8628</v>
+        <v>0.9488</v>
       </c>
       <c r="H13" t="n">
-        <v>0.6897</v>
+        <v>0.3827</v>
       </c>
       <c r="I13" t="n">
-        <v>1.1731</v>
+        <v>0.5661</v>
       </c>
       <c r="J13" t="n">
-        <v>1.8126</v>
+        <v>0.8986</v>
       </c>
       <c r="K13" t="n">
-        <v>1.0438</v>
+        <v>0.7368</v>
       </c>
       <c r="L13" t="n">
-        <v>0.7688</v>
+        <v>0.1619</v>
       </c>
       <c r="M13" t="n">
         <v>0.0502</v>
@@ -1484,6 +1540,11 @@
       </c>
       <c r="X13" t="n">
         <v>-1.2186</v>
+      </c>
+      <c r="Y13" t="inlineStr">
+        <is>
+          <t>play_by_play_2484265_PROCESSED_CHRONO.xlsx</t>
+        </is>
       </c>
     </row>
     <row r="14">
@@ -1563,11 +1624,16 @@
       <c r="X14" t="n">
         <v>0</v>
       </c>
+      <c r="Y14" t="inlineStr">
+        <is>
+          <t>play_by_play_2484265_PROCESSED_CHRONO.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>A. SAMAKE EL ALAOUI</t>
+          <t>G. PÉREZ LAYUNTA</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
@@ -1579,73 +1645,78 @@
         <v>1</v>
       </c>
       <c r="D15" t="n">
-        <v>0.6819</v>
+        <v>1.214</v>
       </c>
       <c r="E15" t="n">
-        <v>-0.6214</v>
+        <v>1.214</v>
       </c>
       <c r="F15" t="n">
-        <v>1.3033</v>
+        <v>0</v>
       </c>
       <c r="G15" t="n">
-        <v>1.0067</v>
+        <v>1.214</v>
       </c>
       <c r="H15" t="n">
-        <v>2.5306</v>
+        <v>0</v>
       </c>
       <c r="I15" t="n">
-        <v>-1.5239</v>
+        <v>1.214</v>
       </c>
       <c r="J15" t="n">
-        <v>0.9619</v>
+        <v>1.214</v>
       </c>
       <c r="K15" t="n">
-        <v>2.8895</v>
+        <v>0</v>
       </c>
       <c r="L15" t="n">
-        <v>-1.9275</v>
+        <v>1.214</v>
       </c>
       <c r="M15" t="n">
-        <v>0.0448</v>
+        <v>0</v>
       </c>
       <c r="N15" t="n">
-        <v>-0.3589</v>
+        <v>0</v>
       </c>
       <c r="O15" t="n">
-        <v>0.4037</v>
+        <v>0</v>
       </c>
       <c r="P15" t="n">
-        <v>-0.7814</v>
+        <v>0</v>
       </c>
       <c r="Q15" t="n">
-        <v>-1.9534</v>
+        <v>0</v>
       </c>
       <c r="R15" t="n">
-        <v>1.1721</v>
+        <v>0</v>
       </c>
       <c r="S15" t="n">
-        <v>0.1245</v>
+        <v>0</v>
       </c>
       <c r="T15" t="n">
-        <v>-0.5164</v>
+        <v>0</v>
       </c>
       <c r="U15" t="n">
-        <v>0.6409</v>
+        <v>0</v>
       </c>
       <c r="V15" t="n">
-        <v>0.3321</v>
+        <v>0</v>
       </c>
       <c r="W15" t="n">
-        <v>0.8865</v>
+        <v>0</v>
       </c>
       <c r="X15" t="n">
-        <v>-0.5545</v>
+        <v>0</v>
+      </c>
+      <c r="Y15" t="inlineStr">
+        <is>
+          <t>play_by_play_2484265_PROCESSED_CHRONO.xlsx</t>
+        </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>G. RUBIO GRACIA</t>
+          <t>P. MARTÍNEZ FERIA</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -1657,73 +1728,78 @@
         <v>1</v>
       </c>
       <c r="D16" t="n">
-        <v>0.583</v>
+        <v>0.914</v>
       </c>
       <c r="E16" t="n">
-        <v>0.0931</v>
+        <v>0.914</v>
       </c>
       <c r="F16" t="n">
-        <v>0.4899</v>
+        <v>0</v>
       </c>
       <c r="G16" t="n">
-        <v>0.3614</v>
+        <v>0.914</v>
       </c>
       <c r="H16" t="n">
-        <v>0.4285</v>
+        <v>0.307</v>
       </c>
       <c r="I16" t="n">
-        <v>-0.06710000000000001</v>
+        <v>0.607</v>
       </c>
       <c r="J16" t="n">
-        <v>0.3867</v>
+        <v>0.914</v>
       </c>
       <c r="K16" t="n">
-        <v>0.4528</v>
+        <v>0.307</v>
       </c>
       <c r="L16" t="n">
-        <v>-0.06610000000000001</v>
+        <v>0.607</v>
       </c>
       <c r="M16" t="n">
-        <v>-0.0253</v>
+        <v>0</v>
       </c>
       <c r="N16" t="n">
-        <v>-0.0243</v>
+        <v>0</v>
       </c>
       <c r="O16" t="n">
-        <v>-0.001</v>
+        <v>0</v>
       </c>
       <c r="P16" t="n">
-        <v>1.1721</v>
+        <v>0</v>
       </c>
       <c r="Q16" t="n">
         <v>0</v>
       </c>
       <c r="R16" t="n">
-        <v>1.1721</v>
+        <v>0</v>
       </c>
       <c r="S16" t="n">
-        <v>0.5454</v>
+        <v>0</v>
       </c>
       <c r="T16" t="n">
-        <v>-0.2935</v>
+        <v>0</v>
       </c>
       <c r="U16" t="n">
-        <v>0.839</v>
+        <v>0</v>
       </c>
       <c r="V16" t="n">
-        <v>-1.4959</v>
+        <v>0</v>
       </c>
       <c r="W16" t="n">
         <v>0</v>
       </c>
       <c r="X16" t="n">
-        <v>-1.4959</v>
+        <v>0</v>
+      </c>
+      <c r="Y16" t="inlineStr">
+        <is>
+          <t>play_by_play_2484265_PROCESSED_CHRONO.xlsx</t>
+        </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>M. FENÉS HERNÁNDEZ</t>
+          <t>A. SAMAKE EL ALAOUI</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -1735,73 +1811,78 @@
         <v>1</v>
       </c>
       <c r="D17" t="n">
-        <v>0.1953</v>
+        <v>0.6819</v>
       </c>
       <c r="E17" t="n">
-        <v>0</v>
+        <v>-0.6214</v>
       </c>
       <c r="F17" t="n">
-        <v>0.1953</v>
+        <v>1.3033</v>
       </c>
       <c r="G17" t="n">
-        <v>0</v>
+        <v>1.0067</v>
       </c>
       <c r="H17" t="n">
-        <v>0</v>
+        <v>2.5306</v>
       </c>
       <c r="I17" t="n">
-        <v>0</v>
+        <v>-1.5239</v>
       </c>
       <c r="J17" t="n">
-        <v>0</v>
+        <v>0.9619</v>
       </c>
       <c r="K17" t="n">
-        <v>0</v>
+        <v>2.8895</v>
       </c>
       <c r="L17" t="n">
-        <v>0</v>
+        <v>-1.9275</v>
       </c>
       <c r="M17" t="n">
-        <v>0</v>
+        <v>0.0448</v>
       </c>
       <c r="N17" t="n">
-        <v>0</v>
+        <v>-0.3589</v>
       </c>
       <c r="O17" t="n">
-        <v>0</v>
+        <v>0.4037</v>
       </c>
       <c r="P17" t="n">
-        <v>0.1953</v>
+        <v>-0.7814</v>
       </c>
       <c r="Q17" t="n">
-        <v>0</v>
+        <v>-1.9534</v>
       </c>
       <c r="R17" t="n">
-        <v>0.1953</v>
+        <v>1.1721</v>
       </c>
       <c r="S17" t="n">
-        <v>0</v>
+        <v>0.1245</v>
       </c>
       <c r="T17" t="n">
-        <v>0</v>
+        <v>-0.5164</v>
       </c>
       <c r="U17" t="n">
-        <v>0</v>
+        <v>0.6409</v>
       </c>
       <c r="V17" t="n">
-        <v>0</v>
+        <v>0.3321</v>
       </c>
       <c r="W17" t="n">
-        <v>0</v>
+        <v>0.8865</v>
       </c>
       <c r="X17" t="n">
-        <v>0</v>
+        <v>-0.5545</v>
+      </c>
+      <c r="Y17" t="inlineStr">
+        <is>
+          <t>play_by_play_2484265_PROCESSED_CHRONO.xlsx</t>
+        </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>B. MORALES CONILL</t>
+          <t>R. PÉREZ GALINDO</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -1813,58 +1894,58 @@
         <v>1</v>
       </c>
       <c r="D18" t="n">
-        <v>0.1093</v>
+        <v>0.614</v>
       </c>
       <c r="E18" t="n">
-        <v>-0.8902</v>
+        <v>0.614</v>
       </c>
       <c r="F18" t="n">
-        <v>0.9995000000000001</v>
+        <v>0</v>
       </c>
       <c r="G18" t="n">
-        <v>-0.1466</v>
+        <v>0.614</v>
       </c>
       <c r="H18" t="n">
-        <v>-0.2407</v>
+        <v>0.614</v>
       </c>
       <c r="I18" t="n">
-        <v>0.09420000000000001</v>
+        <v>0</v>
       </c>
       <c r="J18" t="n">
-        <v>1.0273</v>
+        <v>0.614</v>
       </c>
       <c r="K18" t="n">
-        <v>0.3927</v>
+        <v>0.614</v>
       </c>
       <c r="L18" t="n">
-        <v>0.6346000000000001</v>
+        <v>0</v>
       </c>
       <c r="M18" t="n">
-        <v>-1.1739</v>
+        <v>0</v>
       </c>
       <c r="N18" t="n">
-        <v>-0.6334</v>
+        <v>0</v>
       </c>
       <c r="O18" t="n">
-        <v>-0.5405</v>
+        <v>0</v>
       </c>
       <c r="P18" t="n">
         <v>0</v>
       </c>
       <c r="Q18" t="n">
-        <v>-1.9534</v>
+        <v>0</v>
       </c>
       <c r="R18" t="n">
-        <v>1.9534</v>
+        <v>0</v>
       </c>
       <c r="S18" t="n">
-        <v>0.2559</v>
+        <v>0</v>
       </c>
       <c r="T18" t="n">
-        <v>0.0359</v>
+        <v>0</v>
       </c>
       <c r="U18" t="n">
-        <v>0.22</v>
+        <v>0</v>
       </c>
       <c r="V18" t="n">
         <v>0</v>
@@ -1874,12 +1955,17 @@
       </c>
       <c r="X18" t="n">
         <v>0</v>
+      </c>
+      <c r="Y18" t="inlineStr">
+        <is>
+          <t>play_by_play_2484265_PROCESSED_CHRONO.xlsx</t>
+        </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>R. PÉREZ GALINDO</t>
+          <t>G. RUBIO GRACIA</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -1891,73 +1977,78 @@
         <v>1</v>
       </c>
       <c r="D19" t="n">
-        <v>0.0435</v>
+        <v>0.583</v>
       </c>
       <c r="E19" t="n">
-        <v>2.8735</v>
+        <v>0.0931</v>
       </c>
       <c r="F19" t="n">
-        <v>-2.83</v>
+        <v>0.4899</v>
       </c>
       <c r="G19" t="n">
-        <v>0.6626</v>
+        <v>0.3614</v>
       </c>
       <c r="H19" t="n">
-        <v>0.0023</v>
+        <v>0.4285</v>
       </c>
       <c r="I19" t="n">
-        <v>0.6603</v>
+        <v>-0.06710000000000001</v>
       </c>
       <c r="J19" t="n">
-        <v>3.0545</v>
+        <v>0.3867</v>
       </c>
       <c r="K19" t="n">
-        <v>1.7191</v>
+        <v>0.4528</v>
       </c>
       <c r="L19" t="n">
-        <v>1.3354</v>
+        <v>-0.06610000000000001</v>
       </c>
       <c r="M19" t="n">
-        <v>-2.3919</v>
+        <v>-0.0253</v>
       </c>
       <c r="N19" t="n">
-        <v>-1.7168</v>
+        <v>-0.0243</v>
       </c>
       <c r="O19" t="n">
-        <v>-0.6751</v>
+        <v>-0.001</v>
       </c>
       <c r="P19" t="n">
-        <v>0.1953</v>
+        <v>1.1721</v>
       </c>
       <c r="Q19" t="n">
-        <v>-0.9767</v>
+        <v>0</v>
       </c>
       <c r="R19" t="n">
         <v>1.1721</v>
       </c>
       <c r="S19" t="n">
-        <v>-0.5372</v>
+        <v>0.5454</v>
       </c>
       <c r="T19" t="n">
-        <v>-0.4229</v>
+        <v>-0.2935</v>
       </c>
       <c r="U19" t="n">
-        <v>-0.1143</v>
+        <v>0.839</v>
       </c>
       <c r="V19" t="n">
-        <v>-0.2772</v>
+        <v>-1.4959</v>
       </c>
       <c r="W19" t="n">
-        <v>1.2186</v>
+        <v>0</v>
       </c>
       <c r="X19" t="n">
         <v>-1.4959</v>
+      </c>
+      <c r="Y19" t="inlineStr">
+        <is>
+          <t>play_by_play_2484265_PROCESSED_CHRONO.xlsx</t>
+        </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>M. OBIOLS PUIG</t>
+          <t>M. FENES HERNANDEZ</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
@@ -1969,73 +2060,78 @@
         <v>1</v>
       </c>
       <c r="D20" t="n">
-        <v>-4.3858</v>
+        <v>0.1953</v>
       </c>
       <c r="E20" t="n">
-        <v>-4.0135</v>
+        <v>0</v>
       </c>
       <c r="F20" t="n">
-        <v>-0.3723</v>
+        <v>0.1953</v>
       </c>
       <c r="G20" t="n">
-        <v>-1.5838</v>
+        <v>0</v>
       </c>
       <c r="H20" t="n">
-        <v>-1.3001</v>
+        <v>0</v>
       </c>
       <c r="I20" t="n">
-        <v>-0.2837</v>
+        <v>0</v>
       </c>
       <c r="J20" t="n">
-        <v>-1.7781</v>
+        <v>0</v>
       </c>
       <c r="K20" t="n">
-        <v>-1.2254</v>
+        <v>0</v>
       </c>
       <c r="L20" t="n">
-        <v>-0.5527</v>
+        <v>0</v>
       </c>
       <c r="M20" t="n">
-        <v>0.1944</v>
+        <v>0</v>
       </c>
       <c r="N20" t="n">
-        <v>-0.0747</v>
+        <v>0</v>
       </c>
       <c r="O20" t="n">
-        <v>0.269</v>
+        <v>0</v>
       </c>
       <c r="P20" t="n">
-        <v>-1.5627</v>
+        <v>0.1953</v>
       </c>
       <c r="Q20" t="n">
-        <v>-1.9534</v>
+        <v>0</v>
       </c>
       <c r="R20" t="n">
-        <v>0.3907</v>
+        <v>0.1953</v>
       </c>
       <c r="S20" t="n">
-        <v>-0.0207</v>
+        <v>0</v>
       </c>
       <c r="T20" t="n">
-        <v>-0.282</v>
+        <v>0</v>
       </c>
       <c r="U20" t="n">
-        <v>0.2613</v>
+        <v>0</v>
       </c>
       <c r="V20" t="n">
-        <v>-1.2186</v>
+        <v>0</v>
       </c>
       <c r="W20" t="n">
         <v>0</v>
       </c>
       <c r="X20" t="n">
-        <v>-1.2186</v>
+        <v>0</v>
+      </c>
+      <c r="Y20" t="inlineStr">
+        <is>
+          <t>play_by_play_2484265_PROCESSED_CHRONO.xlsx</t>
+        </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>G. PÉREZ LAYUNTA</t>
+          <t>B. MORALES CONILL</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
@@ -2047,73 +2143,78 @@
         <v>1</v>
       </c>
       <c r="D21" t="n">
-        <v>-4.52</v>
+        <v>0.1093</v>
       </c>
       <c r="E21" t="n">
-        <v>-3.0056</v>
+        <v>-0.8902</v>
       </c>
       <c r="F21" t="n">
-        <v>-1.5143</v>
+        <v>0.9995000000000001</v>
       </c>
       <c r="G21" t="n">
-        <v>-2.2977</v>
+        <v>-0.1466</v>
       </c>
       <c r="H21" t="n">
-        <v>-1.2049</v>
+        <v>-0.2407</v>
       </c>
       <c r="I21" t="n">
-        <v>-1.0928</v>
+        <v>0.09420000000000001</v>
       </c>
       <c r="J21" t="n">
-        <v>0.2992</v>
+        <v>1.0273</v>
       </c>
       <c r="K21" t="n">
-        <v>0.3121</v>
+        <v>0.3927</v>
       </c>
       <c r="L21" t="n">
-        <v>-0.0128</v>
+        <v>0.6346000000000001</v>
       </c>
       <c r="M21" t="n">
-        <v>-2.5969</v>
+        <v>-1.1739</v>
       </c>
       <c r="N21" t="n">
-        <v>-1.517</v>
+        <v>-0.6334</v>
       </c>
       <c r="O21" t="n">
-        <v>-1.0799</v>
+        <v>-0.5405</v>
       </c>
       <c r="P21" t="n">
-        <v>-1.7581</v>
+        <v>0</v>
       </c>
       <c r="Q21" t="n">
-        <v>-2.9301</v>
+        <v>-1.9534</v>
       </c>
       <c r="R21" t="n">
-        <v>1.1721</v>
+        <v>1.9534</v>
       </c>
       <c r="S21" t="n">
-        <v>0.1452</v>
+        <v>0.2559</v>
       </c>
       <c r="T21" t="n">
-        <v>-0.3747</v>
+        <v>0.0359</v>
       </c>
       <c r="U21" t="n">
-        <v>0.5199</v>
+        <v>0.22</v>
       </c>
       <c r="V21" t="n">
-        <v>-0.6093</v>
+        <v>0</v>
       </c>
       <c r="W21" t="n">
         <v>0</v>
       </c>
       <c r="X21" t="n">
-        <v>-0.6093</v>
+        <v>0</v>
+      </c>
+      <c r="Y21" t="inlineStr">
+        <is>
+          <t>play_by_play_2484265_PROCESSED_CHRONO.xlsx</t>
+        </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>F. LLORENS LLAURADO</t>
+          <t>R. PEREZ GALINDO</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
@@ -2125,73 +2226,78 @@
         <v>1</v>
       </c>
       <c r="D22" t="n">
-        <v>-4.9364</v>
+        <v>-0.5705</v>
       </c>
       <c r="E22" t="n">
-        <v>-3.7804</v>
+        <v>2.2595</v>
       </c>
       <c r="F22" t="n">
-        <v>-1.156</v>
+        <v>-2.83</v>
       </c>
       <c r="G22" t="n">
-        <v>-1.862</v>
+        <v>0.0486</v>
       </c>
       <c r="H22" t="n">
-        <v>0.1745</v>
+        <v>-0.6117</v>
       </c>
       <c r="I22" t="n">
-        <v>-2.0365</v>
+        <v>0.6603</v>
       </c>
       <c r="J22" t="n">
-        <v>-0.838</v>
+        <v>2.4405</v>
       </c>
       <c r="K22" t="n">
-        <v>0.3888</v>
+        <v>1.1051</v>
       </c>
       <c r="L22" t="n">
-        <v>-1.2268</v>
+        <v>1.3354</v>
       </c>
       <c r="M22" t="n">
-        <v>-1.0241</v>
+        <v>-2.3919</v>
       </c>
       <c r="N22" t="n">
-        <v>-0.2144</v>
+        <v>-1.7168</v>
       </c>
       <c r="O22" t="n">
-        <v>-0.8097</v>
+        <v>-0.6751</v>
       </c>
       <c r="P22" t="n">
-        <v>-2.1488</v>
+        <v>0.1953</v>
       </c>
       <c r="Q22" t="n">
-        <v>-2.9301</v>
+        <v>-0.9767</v>
       </c>
       <c r="R22" t="n">
-        <v>0.7814</v>
+        <v>1.1721</v>
       </c>
       <c r="S22" t="n">
-        <v>0.293</v>
+        <v>-0.5372</v>
       </c>
       <c r="T22" t="n">
-        <v>-0.0123</v>
+        <v>-0.4229</v>
       </c>
       <c r="U22" t="n">
-        <v>0.3053</v>
+        <v>-0.1143</v>
       </c>
       <c r="V22" t="n">
-        <v>-1.2186</v>
+        <v>-0.2772</v>
       </c>
       <c r="W22" t="n">
-        <v>0</v>
+        <v>1.2186</v>
       </c>
       <c r="X22" t="n">
-        <v>-1.2186</v>
+        <v>-1.4959</v>
+      </c>
+      <c r="Y22" t="inlineStr">
+        <is>
+          <t>play_by_play_2484265_PROCESSED_CHRONO.xlsx</t>
+        </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>--- TOTAL ---</t>
+          <t>M. OBIOLS PUIG</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
@@ -2203,68 +2309,318 @@
         <v>1</v>
       </c>
       <c r="D23" t="n">
-        <v>-1.990799999999997</v>
+        <v>-4.3858</v>
       </c>
       <c r="E23" t="n">
-        <v>-0.07370000000000188</v>
+        <v>-4.0135</v>
       </c>
       <c r="F23" t="n">
+        <v>-0.3723</v>
+      </c>
+      <c r="G23" t="n">
+        <v>-1.5838</v>
+      </c>
+      <c r="H23" t="n">
+        <v>-1.3001</v>
+      </c>
+      <c r="I23" t="n">
+        <v>-0.2837</v>
+      </c>
+      <c r="J23" t="n">
+        <v>-1.7781</v>
+      </c>
+      <c r="K23" t="n">
+        <v>-1.2254</v>
+      </c>
+      <c r="L23" t="n">
+        <v>-0.5527</v>
+      </c>
+      <c r="M23" t="n">
+        <v>0.1944</v>
+      </c>
+      <c r="N23" t="n">
+        <v>-0.0747</v>
+      </c>
+      <c r="O23" t="n">
+        <v>0.269</v>
+      </c>
+      <c r="P23" t="n">
+        <v>-1.5627</v>
+      </c>
+      <c r="Q23" t="n">
+        <v>-1.9534</v>
+      </c>
+      <c r="R23" t="n">
+        <v>0.3907</v>
+      </c>
+      <c r="S23" t="n">
+        <v>-0.0207</v>
+      </c>
+      <c r="T23" t="n">
+        <v>-0.282</v>
+      </c>
+      <c r="U23" t="n">
+        <v>0.2613</v>
+      </c>
+      <c r="V23" t="n">
+        <v>-1.2186</v>
+      </c>
+      <c r="W23" t="n">
+        <v>0</v>
+      </c>
+      <c r="X23" t="n">
+        <v>-1.2186</v>
+      </c>
+      <c r="Y23" t="inlineStr">
+        <is>
+          <t>play_by_play_2484265_PROCESSED_CHRONO.xlsx</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="inlineStr">
+        <is>
+          <t>F. LLORENS LLAURADO</t>
+        </is>
+      </c>
+      <c r="B24" t="inlineStr">
+        <is>
+          <t>CB. CORNELLÀ</t>
+        </is>
+      </c>
+      <c r="C24" t="n">
+        <v>1</v>
+      </c>
+      <c r="D24" t="n">
+        <v>-4.9364</v>
+      </c>
+      <c r="E24" t="n">
+        <v>-3.7804</v>
+      </c>
+      <c r="F24" t="n">
+        <v>-1.156</v>
+      </c>
+      <c r="G24" t="n">
+        <v>-1.862</v>
+      </c>
+      <c r="H24" t="n">
+        <v>0.1745</v>
+      </c>
+      <c r="I24" t="n">
+        <v>-2.0365</v>
+      </c>
+      <c r="J24" t="n">
+        <v>-0.838</v>
+      </c>
+      <c r="K24" t="n">
+        <v>0.3888</v>
+      </c>
+      <c r="L24" t="n">
+        <v>-1.2268</v>
+      </c>
+      <c r="M24" t="n">
+        <v>-1.0241</v>
+      </c>
+      <c r="N24" t="n">
+        <v>-0.2144</v>
+      </c>
+      <c r="O24" t="n">
+        <v>-0.8097</v>
+      </c>
+      <c r="P24" t="n">
+        <v>-2.1488</v>
+      </c>
+      <c r="Q24" t="n">
+        <v>-2.9301</v>
+      </c>
+      <c r="R24" t="n">
+        <v>0.7814</v>
+      </c>
+      <c r="S24" t="n">
+        <v>0.293</v>
+      </c>
+      <c r="T24" t="n">
+        <v>-0.0123</v>
+      </c>
+      <c r="U24" t="n">
+        <v>0.3053</v>
+      </c>
+      <c r="V24" t="n">
+        <v>-1.2186</v>
+      </c>
+      <c r="W24" t="n">
+        <v>0</v>
+      </c>
+      <c r="X24" t="n">
+        <v>-1.2186</v>
+      </c>
+      <c r="Y24" t="inlineStr">
+        <is>
+          <t>play_by_play_2484265_PROCESSED_CHRONO.xlsx</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="inlineStr">
+        <is>
+          <t>G. PEREZ LAYUNTA</t>
+        </is>
+      </c>
+      <c r="B25" t="inlineStr">
+        <is>
+          <t>CB. CORNELLÀ</t>
+        </is>
+      </c>
+      <c r="C25" t="n">
+        <v>1</v>
+      </c>
+      <c r="D25" t="n">
+        <v>-5.7339</v>
+      </c>
+      <c r="E25" t="n">
+        <v>-4.2196</v>
+      </c>
+      <c r="F25" t="n">
+        <v>-1.5143</v>
+      </c>
+      <c r="G25" t="n">
+        <v>-3.5117</v>
+      </c>
+      <c r="H25" t="n">
+        <v>-1.2049</v>
+      </c>
+      <c r="I25" t="n">
+        <v>-2.3067</v>
+      </c>
+      <c r="J25" t="n">
+        <v>-0.9147</v>
+      </c>
+      <c r="K25" t="n">
+        <v>0.3121</v>
+      </c>
+      <c r="L25" t="n">
+        <v>-1.2268</v>
+      </c>
+      <c r="M25" t="n">
+        <v>-2.5969</v>
+      </c>
+      <c r="N25" t="n">
+        <v>-1.517</v>
+      </c>
+      <c r="O25" t="n">
+        <v>-1.0799</v>
+      </c>
+      <c r="P25" t="n">
+        <v>-1.7581</v>
+      </c>
+      <c r="Q25" t="n">
+        <v>-2.9301</v>
+      </c>
+      <c r="R25" t="n">
+        <v>1.1721</v>
+      </c>
+      <c r="S25" t="n">
+        <v>0.1452</v>
+      </c>
+      <c r="T25" t="n">
+        <v>-0.3747</v>
+      </c>
+      <c r="U25" t="n">
+        <v>0.5199</v>
+      </c>
+      <c r="V25" t="n">
+        <v>-0.6093</v>
+      </c>
+      <c r="W25" t="n">
+        <v>0</v>
+      </c>
+      <c r="X25" t="n">
+        <v>-0.6093</v>
+      </c>
+      <c r="Y25" t="inlineStr">
+        <is>
+          <t>play_by_play_2484265_PROCESSED_CHRONO.xlsx</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" t="inlineStr">
+        <is>
+          <t>--- TOTAL ---</t>
+        </is>
+      </c>
+      <c r="B26" t="inlineStr">
+        <is>
+          <t>CB. CORNELLÀ</t>
+        </is>
+      </c>
+      <c r="C26" t="n">
+        <v>1</v>
+      </c>
+      <c r="D26" t="n">
+        <v>-1.990700000000003</v>
+      </c>
+      <c r="E26" t="n">
+        <v>-0.07359999999999811</v>
+      </c>
+      <c r="F26" t="n">
         <v>-1.9172</v>
       </c>
-      <c r="G23" t="n">
-        <v>6.0911</v>
-      </c>
-      <c r="H23" t="n">
-        <v>2.046700000000001</v>
-      </c>
-      <c r="I23" t="n">
-        <v>4.044600000000001</v>
-      </c>
-      <c r="J23" t="n">
-        <v>12.7336</v>
-      </c>
-      <c r="K23" t="n">
+      <c r="G26" t="n">
+        <v>6.091100000000003</v>
+      </c>
+      <c r="H26" t="n">
+        <v>2.0467</v>
+      </c>
+      <c r="I26" t="n">
+        <v>4.0447</v>
+      </c>
+      <c r="J26" t="n">
+        <v>12.7337</v>
+      </c>
+      <c r="K26" t="n">
         <v>8.681199999999999</v>
       </c>
-      <c r="L23" t="n">
-        <v>4.0525</v>
-      </c>
-      <c r="M23" t="n">
-        <v>-6.642500000000001</v>
-      </c>
-      <c r="N23" t="n">
-        <v>-6.6345</v>
-      </c>
-      <c r="O23" t="n">
-        <v>-0.007900000000000129</v>
-      </c>
-      <c r="P23" t="n">
-        <v>-4.883699999999999</v>
-      </c>
-      <c r="Q23" t="n">
+      <c r="L26" t="n">
+        <v>4.052600000000001</v>
+      </c>
+      <c r="M26" t="n">
+        <v>-6.6425</v>
+      </c>
+      <c r="N26" t="n">
+        <v>-6.634500000000001</v>
+      </c>
+      <c r="O26" t="n">
+        <v>-0.007900000000000018</v>
+      </c>
+      <c r="P26" t="n">
+        <v>-4.8837</v>
+      </c>
+      <c r="Q26" t="n">
         <v>-15.6272</v>
       </c>
-      <c r="R23" t="n">
+      <c r="R26" t="n">
         <v>10.744</v>
       </c>
-      <c r="S23" t="n">
+      <c r="S26" t="n">
         <v>1.9534</v>
       </c>
-      <c r="T23" t="n">
+      <c r="T26" t="n">
         <v>-1.058</v>
       </c>
-      <c r="U23" t="n">
+      <c r="U26" t="n">
         <v>3.0116</v>
       </c>
-      <c r="V23" t="n">
+      <c r="V26" t="n">
         <v>-5.1517</v>
       </c>
-      <c r="W23" t="n">
+      <c r="W26" t="n">
         <v>3.8781</v>
       </c>
-      <c r="X23" t="n">
+      <c r="X26" t="n">
         <v>-9.029999999999999</v>
       </c>
+      <c r="Y26" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
